--- a/outputs/Block2_National_Outcome_Summary_v12.xlsx
+++ b/outputs/Block2_National_Outcome_Summary_v12.xlsx
@@ -507,7 +507,7 @@
         <v>4.526479999999951</v>
       </c>
       <c r="D5">
-        <v>-0.2280799999999383</v>
+        <v>-0.2280799999999382</v>
       </c>
       <c r="E5">
         <v>5</v>
@@ -861,10 +861,10 @@
         <v>14</v>
       </c>
       <c r="C26">
-        <v>6.105200000000002</v>
+        <v>6.105200000000003</v>
       </c>
       <c r="D26">
-        <v>-0.6077599999999705</v>
+        <v>-0.6077599999999693</v>
       </c>
       <c r="E26">
         <v>5</v>
@@ -1102,7 +1102,7 @@
         <v>5.273583577922919</v>
       </c>
       <c r="D40">
-        <v>-0.4535257593620535</v>
+        <v>-0.4535257593620557</v>
       </c>
       <c r="E40">
         <v>5</v>
